--- a/output/laminas_provinciales/prov_i_ingr_a_2022_magallanes.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2022_magallanes.xlsx
@@ -71,7 +71,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:03</t>
+    <t xml:space="preserve">2026-09-09 21:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_ingr_a_2022_magallanes.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2022_magallanes.xlsx
@@ -12,13 +12,13 @@
     <sheet name="Serie" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Serie'!$A$1:$C$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Serie'!$A$1:$C$16</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t xml:space="preserve">Provincia</t>
   </si>
@@ -56,6 +56,9 @@
     <t xml:space="preserve">Tierra del Fuego</t>
   </si>
   <si>
+    <t xml:space="preserve">Promedio Regional</t>
+  </si>
+  <si>
     <t xml:space="preserve">Antártica Chilena</t>
   </si>
   <si>
@@ -71,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 21:58</t>
+    <t xml:space="preserve">2026-09-17 13:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -482,7 +485,7 @@
     <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="10.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="11.71" hidden="0" customWidth="1"/>
   </cols>
@@ -524,7 +527,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -541,7 +544,7 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -558,7 +561,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -575,7 +578,7 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -592,7 +595,7 @@
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -609,7 +612,7 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -620,13 +623,19 @@
         <v>8</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1030369</v>
-      </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
+        <v>975640.38</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>896484.56</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>79155.82</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>8.83</v>
+      </c>
       <c r="G8" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -637,13 +646,19 @@
         <v>9</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1191715.12</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+        <v>1179800.75</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>1053378</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>126422.75</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>12</v>
+      </c>
       <c r="G9" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -654,13 +669,19 @@
         <v>10</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1108398.12</v>
-      </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
+        <v>1086518.88</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>982582.94</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>103935.94</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>10.58</v>
+      </c>
       <c r="G10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -671,13 +692,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>983866.44</v>
+        <v>1030369</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -688,13 +709,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>1214538.5</v>
+        <v>1191715.12</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -705,17 +726,68 @@
         <v>10</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>1108765.38</v>
+        <v>1108398.12</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>983866.44</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>1214538.5</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>1108765.38</v>
+      </c>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G13"/>
+  <autoFilter ref="A1:G16"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -732,58 +804,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -806,15 +878,15 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1108398.12</v>
+        <v>1108765.38</v>
       </c>
     </row>
     <row r="3">
@@ -822,7 +894,7 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1108765.38</v>
+        <v>1108398.12</v>
       </c>
     </row>
     <row r="4">
@@ -863,43 +935,43 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1108398.12</v>
+        <v>1108765.38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1241519.62</v>
+        <v>1237020.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1399202.38</v>
+        <v>1322182</v>
       </c>
     </row>
     <row r="5">
@@ -907,10 +979,10 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1108765.38</v>
+        <v>1108398.12</v>
       </c>
     </row>
     <row r="6">
@@ -918,10 +990,10 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1237020.5</v>
+        <v>1241519.62</v>
       </c>
     </row>
     <row r="7">
@@ -929,10 +1001,10 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1322182</v>
+        <v>1399202.38</v>
       </c>
     </row>
     <row r="8">
@@ -940,7 +1012,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>1053178</v>
@@ -951,7 +1023,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>1171853</v>
@@ -962,7 +1034,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>1206815.62</v>
@@ -973,7 +1045,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>979525.25</v>
@@ -984,7 +1056,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>1099123.75</v>
@@ -995,14 +1067,47 @@
         <v>7</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>1185241.38</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>1086518.88</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>1212855.12</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>1295862.38</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C13"/>
+  <autoFilter ref="A1:C16"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>

--- a/output/laminas_provinciales/prov_i_ingr_a_2022_magallanes.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2022_magallanes.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:33</t>
+    <t xml:space="preserve">2026-09-25 21:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -629,7 +629,7 @@
         <v>896484.56</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>79155.82</v>
+        <v>79155.81</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>8.83</v>

--- a/output/laminas_provinciales/prov_i_ingr_a_2022_magallanes.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2022_magallanes.xlsx
@@ -6,75 +6,56 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Barras" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Provincias" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Mapa" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Serie" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Sexo" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Serie'!$A$1:$C$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sexo'!$A$1:$D$6</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
-  <si>
-    <t xml:space="preserve">Provincia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">subgrupo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">valor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">valor_prev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">delta_pp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">delta_pct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prov_rank</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+  <si>
+    <t xml:space="preserve">Unidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor anio anterior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frente a la region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frente al anio anterior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Región de Magallanes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magallanes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antártica Chilena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tierra del Fuego</t>
   </si>
   <si>
     <t xml:space="preserve">Última Esperanza</t>
   </si>
   <si>
-    <t xml:space="preserve">Femenino</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Masculino</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tierra del Fuego</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promedio Regional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antártica Chilena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magallanes</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
-    <t xml:space="preserve">Valor</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-25 21:26</t>
+    <t xml:space="preserve">2026-09-28 21:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -92,31 +73,25 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Ingreso de asalariados formales</t>
+    <t xml:space="preserve">I_INGR_a</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Region de Magallanes</t>
-  </si>
-  <si>
     <t xml:space="preserve">Año</t>
   </si>
   <si>
     <t xml:space="preserve">2022</t>
   </si>
   <si>
-    <t xml:space="preserve">ano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">valor_hist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024</t>
+    <t xml:space="preserve">Mujeres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hombres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brecha de las mujeres</t>
   </si>
 </sst>
 </file>
@@ -481,13 +456,11 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="19.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="11.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="22.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="21.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="20.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="25.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -506,288 +479,76 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1086519</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>921546.88</v>
+        <v>982583</v>
       </c>
       <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2" t="n">
-        <v>5</v>
+      <c r="E2" s="2" t="n">
+        <v>10.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>1027271.38</v>
-      </c>
-      <c r="D3" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1108765</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>979525.25</v>
-      </c>
-      <c r="D4" s="2"/>
+      <c r="B4" s="2" t="n">
+        <v>1108398</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>997149.12</v>
-      </c>
-      <c r="D5" s="2"/>
+      <c r="B5" s="2" t="n">
+        <v>1053178</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2" t="n">
+        <v>-3.1</v>
+      </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="2" t="n">
-        <v>1096572.38</v>
-      </c>
-      <c r="D6" s="2"/>
+      <c r="B6" s="2" t="n">
+        <v>979525</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2" t="n">
+        <v>-9.8</v>
+      </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>1053178</v>
-      </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>975640.38</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>896484.56</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>79155.81</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>8.83</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>1179800.75</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>1053378</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>126422.75</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>1086518.88</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>982582.94</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>103935.94</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>10.58</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>1030369</v>
-      </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>1191715.12</v>
-      </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>1108398.12</v>
-      </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>983866.44</v>
-      </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>1214538.5</v>
-      </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>1108765.38</v>
-      </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2" t="n">
-        <v>1</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G16"/>
+  <autoFilter ref="A1:E6"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -804,58 +565,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -869,8 +630,10 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="19.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="22.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="23.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,236 +641,87 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1108765.38</v>
+        <v>975640</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1179801</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>-17.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1108398.12</v>
+        <v>983866</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>1214538</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>-19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1053178</v>
+        <v>1030369</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>1191715</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>-13.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>979525.25</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:B5"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="19.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>1108765.38</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>1237020.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>1322182</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>997149</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1108398.12</v>
+        <v>1096572</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>-9.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>9</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>921547</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1241519.62</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>1399202.38</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>1053178</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>1171853</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>1206815.62</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>979525.25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>1099123.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>1185241.38</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>1086518.88</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>1212855.12</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>1295862.38</v>
+        <v>1027271</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>-10.3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C16"/>
+  <autoFilter ref="A1:D6"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>

--- a/output/laminas_provinciales/prov_i_ingr_a_2022_magallanes.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2022_magallanes.xlsx
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:34</t>
+    <t xml:space="preserve">2026-10-05 07:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -672,7 +672,7 @@
         <v>983866</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1214538</v>
+        <v>1214539</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>-19</v>
